--- a/PaintShop-September2026_kopie.xlsx
+++ b/PaintShop-September2026_kopie.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stichtingfontys-my.sharepoint.com/personal/582755_student_fontys_nl/Documents/Leerjaar 2/Periode 1/Operations Research 5/OR5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="97" documentId="11_3C5A325E12D14DD35BD44A2F14D57A2270643C57" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{981343DD-733D-4428-83F1-34F1F2896BA7}"/>
+  <xr:revisionPtr revIDLastSave="100" documentId="11_3C5A325E12D14DD35BD44A2F14D57A2270643C57" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{727C5379-51FF-41EF-8FCC-2CC285EE3E22}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1088,7 +1088,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="8">
-        <v>27</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15" x14ac:dyDescent="0.2">
@@ -1096,7 +1096,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="8">
-        <v>27</v>
+        <v>30.48</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15" x14ac:dyDescent="0.2">
@@ -1104,7 +1104,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="8">
-        <v>20</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15" x14ac:dyDescent="0.2">
@@ -1276,23 +1276,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="882bdec5-c3ce-4705-9a84-58ed8ad203ea" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010013B620F01982514694878B55267266B0" ma:contentTypeVersion="86" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="74461f5d53f32db2b022b75481ad65d4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="882bdec5-c3ce-4705-9a84-58ed8ad203ea" xmlns:ns3="c6fe3531-949f-4c96-ac1d-b793c48e3f25" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3f35a72610264df809623b370168ef8a" ns2:_="" ns3:_="">
     <xsd:import namespace="882bdec5-c3ce-4705-9a84-58ed8ad203ea"/>
@@ -1519,25 +1502,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2F853DD-D83E-469C-9E1E-915877D838F7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="882bdec5-c3ce-4705-9a84-58ed8ad203ea" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58A6ABA0-C4D6-4A20-974A-2B1B1E891161}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="882bdec5-c3ce-4705-9a84-58ed8ad203ea"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DCD283C-A444-4931-8008-3456731CDA06}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1554,4 +1536,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58A6ABA0-C4D6-4A20-974A-2B1B1E891161}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="882bdec5-c3ce-4705-9a84-58ed8ad203ea"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2F853DD-D83E-469C-9E1E-915877D838F7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>